--- a/stick-world/config/excel/扩张数据.xlsx
+++ b/stick-world/config/excel/扩张数据.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="地块" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="地块信息" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="势力" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="文明差异" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -439,94 +439,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>terrain</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>resources</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>stickmen_types</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>tech_unlocks</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>initial_owner</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>center_x</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>center_y</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>地形</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>资源(逗号分隔)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>本地火柴人族群</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>可解锁科技</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>初始归属</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>中心X</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>中心Y</t>
         </is>
@@ -550,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>food,wood</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -558,6 +558,7 @@
           <t>plain</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>500</t>
@@ -595,11 +596,7 @@
           <t>volcano,giant</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>tech_smelting</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>200</t>
@@ -629,7 +626,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>food,black_pitch</t>
+          <t>black_pitch</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -637,11 +634,7 @@
           <t>source</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>tech_magic_basic</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>700</t>
@@ -679,11 +672,7 @@
           <t>desert,centaur</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>tech_camelry</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>900</t>
@@ -713,7 +702,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>food,wood</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -721,11 +710,7 @@
           <t>ocean</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>tech_sailing</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>300</t>
@@ -755,7 +740,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>wood,food</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -763,11 +748,7 @@
           <t>forest,winged</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>tech_arbalest</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>600</t>
@@ -805,11 +786,7 @@
           <t>ice</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>tech_frost_resist</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>400</t>

--- a/stick-world/config/excel/扩张数据.xlsx
+++ b/stick-world/config/excel/扩张数据.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="地块信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="势力" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="文明差异" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="regions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="factions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="civ_differences" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,301 +441,266 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name_zh</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>terrain</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>resources</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>stickmen_types</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tech_unlocks</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>initial_owner</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>center_x</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>center_y</t>
+          <t>#output_dir: expansion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>name_zh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>地形</t>
+          <t>terrain</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>资源(逗号分隔)</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>本地火柴人族群</t>
+          <t>stickmen_types</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>可解锁科技</t>
+          <t>tech_unlocks</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>初始归属</t>
+          <t>initial_owner</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>中心X</t>
+          <t>center_x</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>中心Y</t>
+          <t>center_y</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>reg_plain_01</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中原平原</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>plain</t>
+          <t>地形</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>资源(逗号分隔)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>plain</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>本地火柴人族群</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>可解锁科技</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>初始归属</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>中心X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>中心Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>reg_volcano_01</t>
+          <t>reg_plain_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>炎炉山脉</t>
+          <t>中原平原</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>metal,black_pitch</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>volcano,giant</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>plain</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>500</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>reg_source_01</t>
+          <t>reg_volcano_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>源流湿地</t>
+          <t>炎炉山脉</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>swamp</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>black_pitch</t>
+          <t>metal,black_pitch</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>volcano,giant</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>reg_desert_01</t>
+          <t>reg_source_01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>赤砂荒原</t>
+          <t>源流湿地</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>desert</t>
+          <t>swamp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>stone</t>
+          <t>black_pitch</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>desert,centaur</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>source</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>700</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reg_ocean_01</t>
+          <t>reg_desert_01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>碧波群岛</t>
+          <t>赤砂荒原</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>desert</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ocean</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>desert,centaur</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>900</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reg_forest_01</t>
+          <t>reg_ocean_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>苍翠密林</t>
+          <t>碧波群岛</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>forest</t>
+          <t>coast</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -745,54 +710,89 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>forest,winged</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>ocean</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>800</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>reg_forest_01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>苍翠密林</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>forest</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>forest,winged</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>reg_ice_01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>极北冰原</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>ice</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>stone,black_pitch</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>ice</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -821,110 +821,85 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#output_dir: expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>civilization_type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>start_region</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>color_hex</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>势力名</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>文明类型</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>起始地块</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>颜色</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>描述</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fac_plain</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>平原王国</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>agriculture</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>reg_plain_01</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>#4CAF50</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>平原农耕文明，人口众多</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fac_volcano</t>
+          <t>fac_plain</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>炎炉部落</t>
+          <t>平原王国</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -934,29 +909,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>reg_volcano_01</t>
+          <t>reg_plain_01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>#FF5722</t>
+          <t>#4CAF50</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>火山锻造文明，军工发达</t>
+          <t>平原农耕文明，人口众多</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fac_source</t>
+          <t>fac_volcano</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>源流学院</t>
+          <t>炎炉部落</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,143 +941,175 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>reg_source_01</t>
+          <t>reg_volcano_01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>#9C27B0</t>
+          <t>#FF5722</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>法术文明，法师比例极高</t>
+          <t>火山锻造文明，军工发达</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fac_desert</t>
+          <t>fac_source</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>赤砂汗国</t>
+          <t>源流学院</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nomadic</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>reg_desert_01</t>
+          <t>reg_source_01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>#FFC107</t>
+          <t>#9C27B0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>游牧文明，骑兵精锐</t>
+          <t>法术文明，法师比例极高</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fac_ocean</t>
+          <t>fac_desert</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>碧波联邦</t>
+          <t>赤砂汗国</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>nomadic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>reg_ocean_01</t>
+          <t>reg_desert_01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>#2196F3</t>
+          <t>#FFC107</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>海洋贸易文明，造船发达</t>
+          <t>游牧文明，骑兵精锐</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fac_forest</t>
+          <t>fac_ocean</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>苍翠猎团</t>
+          <t>碧波联邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>agriculture</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>reg_forest_01</t>
+          <t>reg_ocean_01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>#4CAF50</t>
+          <t>#2196F3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>森林狩猎文明，隐匿强弓</t>
+          <t>海洋贸易文明，造船发达</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>fac_forest</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>苍翠猎团</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>reg_forest_01</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>#4CAF50</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>森林狩猎文明，隐匿强弓</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>fac_ice</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>极北城邦</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>agriculture</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>reg_ice_01</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>#90CAF9</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>冰原生存专家，防御型文明</t>
         </is>
@@ -1119,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1132,222 +1139,229 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#output_dir: expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>civilization_type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>org_depth_bonus</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>military_bonus</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>economy_bonus</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>research_bonus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>naval_bonus</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>文明类型</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>组织层级倾向</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>军事加成</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>经济加成</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>科研加成</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>海军加成</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>描述</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>agriculture</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>balanced</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>农耕文明组织严密，中央集权</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nomadic</t>
+          <t>agriculture</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>shallow</t>
+          <t>deep</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>高(骑兵)</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>低</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>游牧来去如风，层级灵活</t>
+          <t>农耕文明组织严密，中央集权</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>nomadic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>shallow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>高(骑兵)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>低</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>无</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>商业文明贸易驱动，军事靠外包</t>
+          <t>游牧来去如风，层级灵活</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>商业文明贸易驱动，军事靠外包</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>ocean</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>高(贸易)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>海洋文明制海权至上</t>
         </is>

--- a/stick-world/config/excel/扩张数据.xlsx
+++ b/stick-world/config/excel/扩张数据.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,22 +473,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>center_x</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>center_y</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>tech_unlocks</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>initial_owner</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>center_x</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>center_y</t>
         </is>
       </c>
     </row>
@@ -520,22 +515,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>中心X</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>中心Y</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>可解锁科技</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>初始归属</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>中心X</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>中心Y</t>
         </is>
       </c>
     </row>
@@ -557,7 +547,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>food,wood</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -565,15 +555,11 @@
           <t>plain</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="F4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="5">
@@ -602,14 +588,15 @@
           <t>volcano,giant</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>200</v>
+      </c>
+      <c r="G5" t="n">
+        <v>300</v>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>300</t>
+          <t>tech_smelting</t>
         </is>
       </c>
     </row>
@@ -631,7 +618,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>black_pitch</t>
+          <t>food,black_pitch</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -639,14 +626,15 @@
           <t>source</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>700</v>
+      </c>
+      <c r="G6" t="n">
+        <v>200</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
+          <t>tech_magic_basic</t>
         </is>
       </c>
     </row>
@@ -676,14 +664,15 @@
           <t>desert,centaur</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>900</v>
+      </c>
+      <c r="G7" t="n">
+        <v>600</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>600</t>
+          <t>tech_camelry</t>
         </is>
       </c>
     </row>
@@ -705,7 +694,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>food,wood</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -713,14 +702,15 @@
           <t>ocean</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" t="n">
+        <v>800</v>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>800</t>
+          <t>tech_sailing</t>
         </is>
       </c>
     </row>
@@ -742,7 +732,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>wood,food</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -750,14 +740,15 @@
           <t>forest,winged</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G9" t="n">
+        <v>700</v>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>700</t>
+          <t>tech_arbalest</t>
         </is>
       </c>
     </row>
@@ -787,14 +778,15 @@
           <t>ice</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>tech_frost_resist</t>
         </is>
       </c>
     </row>
@@ -828,64 +820,64 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>name_zh</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>civilization_type</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>start_region</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>color_hex</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>唯一ID</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>势力名</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>文明类型</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>起始地块</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>颜色</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -1146,74 +1138,74 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>civilization_type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>org_depth_bonus</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>military_bonus</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>economy_bonus</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>research_bonus</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>naval_bonus</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>文明类型</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>组织层级倾向</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>军事加成</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>经济加成</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>科研加成</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>海军加成</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
